--- a/data/xlsx/bjma--industry-supervisor.xlsx
+++ b/data/xlsx/bjma--industry-supervisor.xlsx
@@ -697,7 +697,9 @@
       <c r="C16" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="44" t="n"/>
+      <c r="D16" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="44" t="n">
         <v>5</v>
       </c>
@@ -719,7 +721,9 @@
       <c r="C17" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="44" t="n"/>
+      <c r="D17" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="44" t="n">
         <v>5</v>
       </c>
@@ -741,7 +745,9 @@
       <c r="C18" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="44" t="n"/>
+      <c r="D18" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="44" t="n">
         <v>4</v>
       </c>
@@ -763,7 +769,9 @@
       <c r="C19" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="44" t="n"/>
+      <c r="D19" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="44" t="n">
         <v>4</v>
       </c>
@@ -785,7 +793,9 @@
       <c r="C20" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="44" t="n"/>
+      <c r="D20" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="44" t="n">
         <v>3</v>
       </c>
@@ -807,7 +817,9 @@
       <c r="C21" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="44" t="n"/>
+      <c r="D21" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="44" t="n">
         <v>6</v>
       </c>
@@ -829,7 +841,9 @@
       <c r="C22" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="44" t="n"/>
+      <c r="D22" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="44" t="n">
         <v>6</v>
       </c>
@@ -851,7 +865,9 @@
       <c r="C23" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="44" t="n"/>
+      <c r="D23" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="44" t="n">
         <v>7</v>
       </c>
@@ -873,7 +889,9 @@
       <c r="C24" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="44" t="n"/>
+      <c r="D24" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="44" t="n">
         <v>7</v>
       </c>
@@ -895,7 +913,9 @@
       <c r="C25" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="44" t="n"/>
+      <c r="D25" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="44" t="n">
         <v>7</v>
       </c>
@@ -917,7 +937,9 @@
       <c r="C26" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="44" t="n"/>
+      <c r="D26" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="44" t="n">
         <v>6</v>
       </c>
@@ -939,7 +961,9 @@
       <c r="C27" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="44" t="n"/>
+      <c r="D27" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="44" t="n">
         <v>6</v>
       </c>
@@ -961,7 +985,9 @@
       <c r="C28" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="44" t="n"/>
+      <c r="D28" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="44" t="n">
         <v>6</v>
       </c>
@@ -983,7 +1009,9 @@
       <c r="C29" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="44" t="n"/>
+      <c r="D29" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="44" t="n">
         <v>7</v>
       </c>
@@ -1005,7 +1033,9 @@
       <c r="C30" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="44" t="n"/>
+      <c r="D30" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="44" t="n">
         <v>6</v>
       </c>
@@ -1027,7 +1057,9 @@
       <c r="C31" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="44" t="n"/>
+      <c r="D31" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="44" t="n">
         <v>6</v>
       </c>
@@ -1049,7 +1081,9 @@
       <c r="C32" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="44" t="n"/>
+      <c r="D32" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="44" t="n">
         <v>6</v>
       </c>
@@ -1071,7 +1105,9 @@
       <c r="C33" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="44" t="n"/>
+      <c r="D33" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="44" t="n">
         <v>6</v>
       </c>
@@ -1093,7 +1129,9 @@
       <c r="C34" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="44" t="n"/>
+      <c r="D34" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="44" t="n">
         <v>6</v>
       </c>
@@ -1115,7 +1153,9 @@
       <c r="C35" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="44" t="n"/>
+      <c r="D35" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="44" t="n">
         <v>6</v>
       </c>
@@ -1137,7 +1177,9 @@
       <c r="C36" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="44" t="n"/>
+      <c r="D36" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="44" t="n">
         <v>6</v>
       </c>
@@ -1159,7 +1201,9 @@
       <c r="C37" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="44" t="n"/>
+      <c r="D37" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="44" t="n">
         <v>6</v>
       </c>
@@ -1181,7 +1225,9 @@
       <c r="C38" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="44" t="n"/>
+      <c r="D38" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="44" t="n">
         <v>6</v>
       </c>
@@ -1203,7 +1249,9 @@
       <c r="C39" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="44" t="n"/>
+      <c r="D39" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="44" t="n">
         <v>6</v>
       </c>
@@ -1225,7 +1273,9 @@
       <c r="C40" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="44" t="n"/>
+      <c r="D40" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="44" t="n">
         <v>7</v>
       </c>
@@ -1247,7 +1297,9 @@
       <c r="C41" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="44" t="n"/>
+      <c r="D41" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="44" t="n">
         <v>6</v>
       </c>
@@ -1269,7 +1321,9 @@
       <c r="C42" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="44" t="n"/>
+      <c r="D42" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="44" t="n">
         <v>6</v>
       </c>
@@ -1291,7 +1345,9 @@
       <c r="C43" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="44" t="n"/>
+      <c r="D43" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="44" t="n">
         <v>5</v>
       </c>
@@ -1313,7 +1369,9 @@
       <c r="C44" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="44" t="n"/>
+      <c r="D44" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="44" t="n">
         <v>6</v>
       </c>
@@ -1335,7 +1393,9 @@
       <c r="C45" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="D45" s="44" t="n"/>
+      <c r="D45" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="44" t="n">
         <v>4</v>
       </c>
@@ -1357,7 +1417,9 @@
       <c r="C46" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="44" t="n"/>
+      <c r="D46" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="44" t="n">
         <v>3</v>
       </c>
@@ -1379,7 +1441,9 @@
       <c r="C47" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D47" s="44" t="n"/>
+      <c r="D47" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="44" t="n">
         <v>5</v>
       </c>
@@ -1401,7 +1465,9 @@
       <c r="C48" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="44" t="n"/>
+      <c r="D48" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="44" t="n">
         <v>8</v>
       </c>
@@ -1423,7 +1489,9 @@
       <c r="C49" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="44" t="n"/>
+      <c r="D49" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="44" t="n">
         <v>7</v>
       </c>
@@ -1445,7 +1513,9 @@
       <c r="C50" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="44" t="n"/>
+      <c r="D50" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" s="44" t="n">
         <v>8</v>
       </c>
@@ -1467,7 +1537,9 @@
       <c r="C51" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="44" t="n"/>
+      <c r="D51" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" s="44" t="n">
         <v>7</v>
       </c>
@@ -1489,7 +1561,9 @@
       <c r="C52" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="44" t="n"/>
+      <c r="D52" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" s="44" t="n">
         <v>8</v>
       </c>
@@ -1511,7 +1585,9 @@
       <c r="C53" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="D53" s="44" t="n"/>
+      <c r="D53" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E53" s="44" t="n">
         <v>8</v>
       </c>
@@ -1533,7 +1609,9 @@
       <c r="C54" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="44" t="n"/>
+      <c r="D54" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E54" s="44" t="n">
         <v>8</v>
       </c>
@@ -1555,7 +1633,9 @@
       <c r="C55" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D55" s="44" t="n"/>
+      <c r="D55" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E55" s="44" t="n">
         <v>4</v>
       </c>
@@ -1577,7 +1657,9 @@
       <c r="C56" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="44" t="n"/>
+      <c r="D56" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E56" s="44" t="n">
         <v>4</v>
       </c>
@@ -1599,7 +1681,9 @@
       <c r="C57" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="44" t="n"/>
+      <c r="D57" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E57" s="44" t="n">
         <v>4</v>
       </c>
@@ -1621,7 +1705,9 @@
       <c r="C58" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D58" s="44" t="n"/>
+      <c r="D58" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E58" s="44" t="n">
         <v>3</v>
       </c>
@@ -1643,7 +1729,9 @@
       <c r="C59" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="44" t="n"/>
+      <c r="D59" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E59" s="44" t="n">
         <v>4</v>
       </c>
@@ -1665,7 +1753,9 @@
       <c r="C60" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="D60" s="44" t="n"/>
+      <c r="D60" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E60" s="44" t="n">
         <v>3</v>
       </c>
@@ -1687,7 +1777,9 @@
       <c r="C61" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="44" t="n"/>
+      <c r="D61" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E61" s="44" t="n">
         <v>5</v>
       </c>
@@ -1709,7 +1801,9 @@
       <c r="C62" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D62" s="44" t="n"/>
+      <c r="D62" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E62" s="44" t="n">
         <v>6</v>
       </c>
@@ -1731,7 +1825,9 @@
       <c r="C63" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="D63" s="44" t="n"/>
+      <c r="D63" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E63" s="44" t="n">
         <v>5</v>
       </c>
@@ -1753,7 +1849,9 @@
       <c r="C64" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="44" t="n"/>
+      <c r="D64" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E64" s="44" t="n">
         <v>4</v>
       </c>
@@ -1775,7 +1873,9 @@
       <c r="C65" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="44" t="n"/>
+      <c r="D65" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E65" s="44" t="n">
         <v>5</v>
       </c>
